--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-15).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-15).xlsx
@@ -938,94 +938,91 @@
     <t>215</t>
   </si>
   <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>R$ 5.058,14</t>
-  </si>
-  <si>
-    <t>56.5</t>
-  </si>
-  <si>
-    <t>36.2</t>
-  </si>
-  <si>
-    <t>5.28</t>
-  </si>
-  <si>
-    <t>19.2</t>
-  </si>
-  <si>
-    <t>7.6</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>42.1%</t>
-  </si>
-  <si>
-    <t>17.5%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 4.932,90</t>
+  </si>
+  <si>
+    <t>55.0</t>
+  </si>
+  <si>
+    <t>35.7</t>
+  </si>
+  <si>
+    <t>5.32</t>
+  </si>
+  <si>
+    <t>19.6</t>
+  </si>
+  <si>
+    <t>7.9</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>40.2%</t>
+  </si>
+  <si>
+    <t>18.9%</t>
+  </si>
+  <si>
+    <t>1.3%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>4.0%</t>
+    <t>3.9%</t>
   </si>
   <si>
     <t>1.5%</t>
   </si>
   <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>7.1%</t>
-  </si>
-  <si>
-    <t>3.1%</t>
-  </si>
-  <si>
-    <t>4.2%</t>
-  </si>
-  <si>
-    <t>1186.0</t>
-  </si>
-  <si>
-    <t>945.0</t>
-  </si>
-  <si>
-    <t>73.0</t>
-  </si>
-  <si>
-    <t>12.0</t>
+    <t>7.3%</t>
+  </si>
+  <si>
+    <t>3.3%</t>
+  </si>
+  <si>
+    <t>5.4%</t>
+  </si>
+  <si>
+    <t>1536.0</t>
+  </si>
+  <si>
+    <t>1235.0</t>
+  </si>
+  <si>
+    <t>86.0</t>
+  </si>
+  <si>
+    <t>16.0</t>
+  </si>
+  <si>
+    <t>257.0</t>
+  </si>
+  <si>
+    <t>100.0</t>
+  </si>
+  <si>
+    <t>11.0</t>
+  </si>
+  <si>
+    <t>479.0</t>
   </si>
   <si>
     <t>213.0</t>
   </si>
   <si>
-    <t>82.0</t>
-  </si>
-  <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>385.0</t>
-  </si>
-  <si>
-    <t>166.0</t>
-  </si>
-  <si>
-    <t>224.0</t>
-  </si>
-  <si>
-    <t>0.7%</t>
-  </si>
-  <si>
-    <t>36.0</t>
+    <t>353.0</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>37.0</t>
   </si>
   <si>
     <t>1</t>
@@ -3245,7 +3242,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>51</v>
@@ -3275,35 +3272,93 @@
         <v>58</v>
       </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="M13" s="5">
+        <v>6247.6599999999999</v>
+      </c>
+      <c r="N13" s="6">
+        <v>77</v>
+      </c>
+      <c r="O13" s="6">
+        <v>50</v>
+      </c>
+      <c r="P13" s="7">
+        <v>7.1429162500000007</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>20.860333999999998</v>
+      </c>
+      <c r="R13" s="8">
+        <v>6.5720000000000001</v>
+      </c>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -5319,7 +5374,7 @@
         <v>19545</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>51</v>
@@ -5349,35 +5404,93 @@
         <v>58</v>
       </c>
       <c r="L27" s="4"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="9"/>
-      <c r="AD27" s="6"/>
-      <c r="AE27" s="6"/>
-      <c r="AF27" s="6"/>
-      <c r="AG27" s="6"/>
-      <c r="AH27" s="6"/>
-      <c r="AI27" s="6"/>
-      <c r="AJ27" s="6"/>
-      <c r="AK27" s="6"/>
-      <c r="AL27" s="6"/>
-      <c r="AM27" s="6"/>
-      <c r="AN27" s="9"/>
-      <c r="AO27" s="6"/>
+      <c r="M27" s="5">
+        <v>2674.0500000000002</v>
+      </c>
+      <c r="N27" s="6">
+        <v>38</v>
+      </c>
+      <c r="O27" s="6">
+        <v>21</v>
+      </c>
+      <c r="P27" s="7">
+        <v>3.7395843750000002</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>20.3127</v>
+      </c>
+      <c r="R27" s="8">
+        <v>8.7641650000000002</v>
+      </c>
+      <c r="S27" s="8">
+        <v>8</v>
+      </c>
+      <c r="T27" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="U27" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="V27" s="9">
+        <v>0</v>
+      </c>
+      <c r="W27" s="9">
+        <v>0</v>
+      </c>
+      <c r="X27" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="Y27" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="Z27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="AB27" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AC27" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="AD27" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL27" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP27" s="4">
         <v>58</v>
       </c>
@@ -5418,7 +5531,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>51</v>
@@ -5448,35 +5561,93 @@
         <v>58</v>
       </c>
       <c r="L28" s="4"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="6"/>
-      <c r="AE28" s="6"/>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="6"/>
-      <c r="AI28" s="6"/>
-      <c r="AJ28" s="6"/>
-      <c r="AK28" s="6"/>
-      <c r="AL28" s="6"/>
-      <c r="AM28" s="6"/>
-      <c r="AN28" s="9"/>
-      <c r="AO28" s="6"/>
+      <c r="M28" s="5">
+        <v>5495.1999999999998</v>
+      </c>
+      <c r="N28" s="6">
+        <v>53</v>
+      </c>
+      <c r="O28" s="6">
+        <v>28</v>
+      </c>
+      <c r="P28" s="7">
+        <v>2.1305555555555555</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>14.659525</v>
+      </c>
+      <c r="R28" s="8">
+        <v>5.2922607142857148</v>
+      </c>
+      <c r="S28" s="8">
+        <v>7</v>
+      </c>
+      <c r="T28" s="9">
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="U28" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="V28" s="9">
+        <v>0</v>
+      </c>
+      <c r="W28" s="9">
+        <v>0</v>
+      </c>
+      <c r="X28" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="Y28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="AA28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AD28" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP28" s="4">
         <v>58</v>
       </c>
@@ -7083,7 +7254,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>51</v>
@@ -7113,35 +7284,93 @@
         <v>58</v>
       </c>
       <c r="L39" s="4"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="9"/>
-      <c r="AO39" s="6"/>
+      <c r="M39" s="5">
+        <v>7382.3800000000001</v>
+      </c>
+      <c r="N39" s="6">
+        <v>81</v>
+      </c>
+      <c r="O39" s="6">
+        <v>54</v>
+      </c>
+      <c r="P39" s="7">
+        <v>2.3506493506493507</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>13.760494444444443</v>
+      </c>
+      <c r="R39" s="8">
+        <v>5.850407317073171</v>
+      </c>
+      <c r="S39" s="8">
+        <v>8</v>
+      </c>
+      <c r="T39" s="9">
+        <v>0.57407407407407407</v>
+      </c>
+      <c r="U39" s="9">
+        <v>0.42592592592592593</v>
+      </c>
+      <c r="V39" s="9">
+        <v>0.018518518518518517</v>
+      </c>
+      <c r="W39" s="9">
+        <v>0</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>0.092592592592592587</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6">
+        <v>32</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>23</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>6</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="6">
+        <v>18</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
       </c>
@@ -7595,7 +7824,7 @@
         <v>19580</v>
       </c>
       <c r="B43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>51</v>
@@ -7625,35 +7854,93 @@
         <v>58</v>
       </c>
       <c r="L43" s="4"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="6"/>
-      <c r="P43" s="7"/>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="8"/>
-      <c r="S43" s="8"/>
-      <c r="T43" s="9"/>
-      <c r="U43" s="9"/>
-      <c r="V43" s="9"/>
-      <c r="W43" s="9"/>
-      <c r="X43" s="9"/>
-      <c r="Y43" s="9"/>
-      <c r="Z43" s="9"/>
-      <c r="AA43" s="9"/>
-      <c r="AB43" s="9"/>
-      <c r="AC43" s="9"/>
-      <c r="AD43" s="6"/>
-      <c r="AE43" s="6"/>
-      <c r="AF43" s="6"/>
-      <c r="AG43" s="6"/>
-      <c r="AH43" s="6"/>
-      <c r="AI43" s="6"/>
-      <c r="AJ43" s="6"/>
-      <c r="AK43" s="6"/>
-      <c r="AL43" s="6"/>
-      <c r="AM43" s="6"/>
-      <c r="AN43" s="9"/>
-      <c r="AO43" s="6"/>
+      <c r="M43" s="5">
+        <v>7644.8500000000004</v>
+      </c>
+      <c r="N43" s="6">
+        <v>68</v>
+      </c>
+      <c r="O43" s="6">
+        <v>51</v>
+      </c>
+      <c r="P43" s="7">
+        <v>8.6801927536231887</v>
+      </c>
+      <c r="Q43" s="8">
+        <v>29.084641176470591</v>
+      </c>
+      <c r="R43" s="8">
+        <v>13.099019607843136</v>
+      </c>
+      <c r="S43" s="8">
+        <v>7</v>
+      </c>
+      <c r="T43" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="U43" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="V43" s="9">
+        <v>0</v>
+      </c>
+      <c r="W43" s="9">
+        <v>0</v>
+      </c>
+      <c r="X43" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="AB43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP43" s="4">
         <v>58</v>
       </c>
@@ -7694,7 +7981,7 @@
         <v>19581</v>
       </c>
       <c r="B44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C44" s="4">
         <v>51</v>
@@ -7724,35 +8011,93 @@
         <v>58</v>
       </c>
       <c r="L44" s="4"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="6"/>
-      <c r="P44" s="7"/>
-      <c r="Q44" s="8"/>
-      <c r="R44" s="8"/>
-      <c r="S44" s="8"/>
-      <c r="T44" s="9"/>
-      <c r="U44" s="9"/>
-      <c r="V44" s="9"/>
-      <c r="W44" s="9"/>
-      <c r="X44" s="9"/>
-      <c r="Y44" s="9"/>
-      <c r="Z44" s="9"/>
-      <c r="AA44" s="9"/>
-      <c r="AB44" s="9"/>
-      <c r="AC44" s="9"/>
-      <c r="AD44" s="6"/>
-      <c r="AE44" s="6"/>
-      <c r="AF44" s="6"/>
-      <c r="AG44" s="6"/>
-      <c r="AH44" s="6"/>
-      <c r="AI44" s="6"/>
-      <c r="AJ44" s="6"/>
-      <c r="AK44" s="6"/>
-      <c r="AL44" s="6"/>
-      <c r="AM44" s="6"/>
-      <c r="AN44" s="9"/>
-      <c r="AO44" s="6"/>
+      <c r="M44" s="5">
+        <v>6925.0600000000004</v>
+      </c>
+      <c r="N44" s="6">
+        <v>66</v>
+      </c>
+      <c r="O44" s="6">
+        <v>50</v>
+      </c>
+      <c r="P44" s="7">
+        <v>3.388725</v>
+      </c>
+      <c r="Q44" s="8">
+        <v>17.256</v>
+      </c>
+      <c r="R44" s="8">
+        <v>7.0625</v>
+      </c>
+      <c r="S44" s="8">
+        <v>8</v>
+      </c>
+      <c r="T44" s="9">
+        <v>0.52000000000000002</v>
+      </c>
+      <c r="U44" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="V44" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="W44" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="X44" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Y44" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="Z44" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="9">
+        <v>0.16</v>
+      </c>
+      <c r="AB44" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="AD44" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE44" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF44" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG44" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH44" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI44" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="6">
+        <v>8</v>
+      </c>
+      <c r="AL44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM44" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN44" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO44" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP44" s="4">
         <v>58</v>
       </c>
@@ -7950,7 +8295,7 @@
         <v>19596</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>51</v>
@@ -7978,35 +8323,93 @@
         <v>58</v>
       </c>
       <c r="L46" s="4"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="8"/>
-      <c r="R46" s="8"/>
-      <c r="S46" s="8"/>
-      <c r="T46" s="9"/>
-      <c r="U46" s="9"/>
-      <c r="V46" s="9"/>
-      <c r="W46" s="9"/>
-      <c r="X46" s="9"/>
-      <c r="Y46" s="9"/>
-      <c r="Z46" s="9"/>
-      <c r="AA46" s="9"/>
-      <c r="AB46" s="9"/>
-      <c r="AC46" s="9"/>
-      <c r="AD46" s="6"/>
-      <c r="AE46" s="6"/>
-      <c r="AF46" s="6"/>
-      <c r="AG46" s="6"/>
-      <c r="AH46" s="6"/>
-      <c r="AI46" s="6"/>
-      <c r="AJ46" s="6"/>
-      <c r="AK46" s="6"/>
-      <c r="AL46" s="6"/>
-      <c r="AM46" s="6"/>
-      <c r="AN46" s="9"/>
-      <c r="AO46" s="6"/>
+      <c r="M46" s="5">
+        <v>5749.25</v>
+      </c>
+      <c r="N46" s="6">
+        <v>51</v>
+      </c>
+      <c r="O46" s="6">
+        <v>32</v>
+      </c>
+      <c r="P46" s="7">
+        <v>2.5427679245283015</v>
+      </c>
+      <c r="Q46" s="8">
+        <v>15.201040624999999</v>
+      </c>
+      <c r="R46" s="8">
+        <v>6.9827586206896548</v>
+      </c>
+      <c r="S46" s="8">
+        <v>7</v>
+      </c>
+      <c r="T46" s="9">
+        <v>0.53125</v>
+      </c>
+      <c r="U46" s="9">
+        <v>0.21875</v>
+      </c>
+      <c r="V46" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="W46" s="9">
+        <v>0</v>
+      </c>
+      <c r="X46" s="9">
+        <v>0.1875</v>
+      </c>
+      <c r="Y46" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="Z46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="9">
+        <v>0.09375</v>
+      </c>
+      <c r="AB46" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AC46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI46" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP46" s="4">
         <v>58</v>
       </c>
@@ -8514,7 +8917,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>51</v>
@@ -8544,35 +8947,93 @@
         <v>58</v>
       </c>
       <c r="L50" s="4"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
-      <c r="S50" s="8"/>
-      <c r="T50" s="9"/>
-      <c r="U50" s="9"/>
-      <c r="V50" s="9"/>
-      <c r="W50" s="9"/>
-      <c r="X50" s="9"/>
-      <c r="Y50" s="9"/>
-      <c r="Z50" s="9"/>
-      <c r="AA50" s="9"/>
-      <c r="AB50" s="9"/>
-      <c r="AC50" s="9"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="6"/>
-      <c r="AF50" s="6"/>
-      <c r="AG50" s="6"/>
-      <c r="AH50" s="6"/>
-      <c r="AI50" s="6"/>
-      <c r="AJ50" s="6"/>
-      <c r="AK50" s="6"/>
-      <c r="AL50" s="6"/>
-      <c r="AM50" s="6"/>
-      <c r="AN50" s="9"/>
-      <c r="AO50" s="6"/>
+      <c r="M50" s="5">
+        <v>5863.8800000000001</v>
+      </c>
+      <c r="N50" s="6">
+        <v>69</v>
+      </c>
+      <c r="O50" s="6">
+        <v>48</v>
+      </c>
+      <c r="P50" s="7">
+        <v>3.1571032786885249</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>15.077083333333334</v>
+      </c>
+      <c r="R50" s="8">
+        <v>4.2981891304347828</v>
+      </c>
+      <c r="S50" s="8">
+        <v>8</v>
+      </c>
+      <c r="T50" s="9">
+        <v>0.6875</v>
+      </c>
+      <c r="U50" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="V50" s="9">
+        <v>0</v>
+      </c>
+      <c r="W50" s="9">
+        <v>0</v>
+      </c>
+      <c r="X50" s="9">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="Y50" s="9">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="Z50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="AB50" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="AC50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL50" s="6">
+        <v>6</v>
+      </c>
+      <c r="AM50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP50" s="4">
         <v>58</v>
       </c>
@@ -8869,7 +9330,7 @@
         <v>19607</v>
       </c>
       <c r="B53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C53" s="4">
         <v>51</v>
@@ -8897,14 +9358,26 @@
         <v>58</v>
       </c>
       <c r="L53" s="4"/>
-      <c r="M53" s="5"/>
-      <c r="N53" s="6"/>
+      <c r="M53" s="5">
+        <v>5386.8400000000001</v>
+      </c>
+      <c r="N53" s="6">
+        <v>53</v>
+      </c>
       <c r="O53" s="6"/>
-      <c r="P53" s="7"/>
-      <c r="Q53" s="8"/>
-      <c r="R53" s="8"/>
+      <c r="P53" s="7">
+        <v>4.3872549019607847</v>
+      </c>
+      <c r="Q53" s="8">
+        <v>13.347999999999999</v>
+      </c>
+      <c r="R53" s="8">
+        <v>2.901332</v>
+      </c>
       <c r="S53" s="8"/>
-      <c r="T53" s="9"/>
+      <c r="T53" s="9">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="U53" s="9"/>
       <c r="V53" s="9"/>
       <c r="W53" s="9"/>
@@ -8966,7 +9439,7 @@
         <v>19609</v>
       </c>
       <c r="B54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C54" s="4">
         <v>51</v>
@@ -8996,35 +9469,93 @@
         <v>58</v>
       </c>
       <c r="L54" s="4"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="6"/>
-      <c r="O54" s="6"/>
-      <c r="P54" s="7"/>
-      <c r="Q54" s="8"/>
-      <c r="R54" s="8"/>
-      <c r="S54" s="8"/>
-      <c r="T54" s="9"/>
-      <c r="U54" s="9"/>
-      <c r="V54" s="9"/>
-      <c r="W54" s="9"/>
-      <c r="X54" s="9"/>
-      <c r="Y54" s="9"/>
-      <c r="Z54" s="9"/>
-      <c r="AA54" s="9"/>
-      <c r="AB54" s="9"/>
-      <c r="AC54" s="9"/>
-      <c r="AD54" s="6"/>
-      <c r="AE54" s="6"/>
-      <c r="AF54" s="6"/>
-      <c r="AG54" s="6"/>
-      <c r="AH54" s="6"/>
-      <c r="AI54" s="6"/>
-      <c r="AJ54" s="6"/>
-      <c r="AK54" s="6"/>
-      <c r="AL54" s="6"/>
-      <c r="AM54" s="6"/>
-      <c r="AN54" s="9"/>
-      <c r="AO54" s="6"/>
+      <c r="M54" s="5">
+        <v>4513.0500000000002</v>
+      </c>
+      <c r="N54" s="6">
+        <v>47</v>
+      </c>
+      <c r="O54" s="6">
+        <v>37</v>
+      </c>
+      <c r="P54" s="7">
+        <v>6.268402083333334</v>
+      </c>
+      <c r="Q54" s="8">
+        <v>40.222521621621624</v>
+      </c>
+      <c r="R54" s="8">
+        <v>27.006756756756758</v>
+      </c>
+      <c r="S54" s="8">
+        <v>7</v>
+      </c>
+      <c r="T54" s="9">
+        <v>0.10810810810810811</v>
+      </c>
+      <c r="U54" s="9">
+        <v>0.10810810810810811</v>
+      </c>
+      <c r="V54" s="9">
+        <v>0</v>
+      </c>
+      <c r="W54" s="9">
+        <v>0</v>
+      </c>
+      <c r="X54" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="9">
+        <v>0.10810810810810811</v>
+      </c>
+      <c r="AD54" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE54" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM54" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO54" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP54" s="4">
         <v>58</v>
       </c>
@@ -9065,7 +9596,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -9095,35 +9626,93 @@
         <v>58</v>
       </c>
       <c r="L55" s="4"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="8"/>
-      <c r="S55" s="8"/>
-      <c r="T55" s="9"/>
-      <c r="U55" s="9"/>
-      <c r="V55" s="9"/>
-      <c r="W55" s="9"/>
-      <c r="X55" s="9"/>
-      <c r="Y55" s="9"/>
-      <c r="Z55" s="9"/>
-      <c r="AA55" s="9"/>
-      <c r="AB55" s="9"/>
-      <c r="AC55" s="9"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="6"/>
-      <c r="AF55" s="6"/>
-      <c r="AG55" s="6"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="6"/>
-      <c r="AJ55" s="6"/>
-      <c r="AK55" s="6"/>
-      <c r="AL55" s="6"/>
-      <c r="AM55" s="6"/>
-      <c r="AN55" s="9"/>
-      <c r="AO55" s="6"/>
+      <c r="M55" s="5">
+        <v>4514.6999999999998</v>
+      </c>
+      <c r="N55" s="6">
+        <v>55</v>
+      </c>
+      <c r="O55" s="6">
+        <v>45</v>
+      </c>
+      <c r="P55" s="7">
+        <v>2.3593561403508776</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>17.708536585365852</v>
+      </c>
+      <c r="R55" s="8">
+        <v>8.5142268292682921</v>
+      </c>
+      <c r="S55" s="8">
+        <v>7</v>
+      </c>
+      <c r="T55" s="9">
+        <v>0.41463414634146339</v>
+      </c>
+      <c r="U55" s="9">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="V55" s="9">
+        <v>0</v>
+      </c>
+      <c r="W55" s="9">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9">
+        <v>0.044444444444444446</v>
+      </c>
+      <c r="Y55" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="9">
+        <v>0.044444444444444446</v>
+      </c>
+      <c r="AB55" s="9">
+        <v>0.044444444444444446</v>
+      </c>
+      <c r="AC55" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AD55" s="6">
+        <v>21</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>20</v>
+      </c>
+      <c r="AF55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM55" s="6">
+        <v>15</v>
+      </c>
+      <c r="AN55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP55" s="4">
         <v>58</v>
       </c>
@@ -9889,7 +10478,7 @@
         <v>19624</v>
       </c>
       <c r="B61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C61" s="4">
         <v>51</v>
@@ -9917,35 +10506,93 @@
         <v>58</v>
       </c>
       <c r="L61" s="4"/>
-      <c r="M61" s="5"/>
-      <c r="N61" s="6"/>
-      <c r="O61" s="6"/>
-      <c r="P61" s="7"/>
-      <c r="Q61" s="8"/>
-      <c r="R61" s="8"/>
-      <c r="S61" s="8"/>
-      <c r="T61" s="9"/>
-      <c r="U61" s="9"/>
-      <c r="V61" s="9"/>
-      <c r="W61" s="9"/>
-      <c r="X61" s="9"/>
-      <c r="Y61" s="9"/>
-      <c r="Z61" s="9"/>
-      <c r="AA61" s="9"/>
-      <c r="AB61" s="9"/>
-      <c r="AC61" s="9"/>
-      <c r="AD61" s="6"/>
-      <c r="AE61" s="6"/>
-      <c r="AF61" s="6"/>
-      <c r="AG61" s="6"/>
-      <c r="AH61" s="6"/>
-      <c r="AI61" s="6"/>
-      <c r="AJ61" s="6"/>
-      <c r="AK61" s="6"/>
-      <c r="AL61" s="6"/>
-      <c r="AM61" s="6"/>
-      <c r="AN61" s="9"/>
-      <c r="AO61" s="6"/>
+      <c r="M61" s="5">
+        <v>3225.0999999999999</v>
+      </c>
+      <c r="N61" s="6">
+        <v>39</v>
+      </c>
+      <c r="O61" s="6">
+        <v>16</v>
+      </c>
+      <c r="P61" s="7">
+        <v>1.7035078947368421</v>
+      </c>
+      <c r="Q61" s="8">
+        <v>12.343333333333334</v>
+      </c>
+      <c r="R61" s="8">
+        <v>4.5607142857142859</v>
+      </c>
+      <c r="S61" s="8">
+        <v>7</v>
+      </c>
+      <c r="T61" s="9">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="U61" s="9">
+        <v>0.3125</v>
+      </c>
+      <c r="V61" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="W61" s="9">
+        <v>0</v>
+      </c>
+      <c r="X61" s="9">
+        <v>0.3125</v>
+      </c>
+      <c r="Y61" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="Z61" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="AB61" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE61" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF61" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG61" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI61" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ61" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL61" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP61" s="4">
         <v>58</v>
       </c>
@@ -11333,7 +11980,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>51</v>
@@ -11361,35 +12008,93 @@
         <v>58</v>
       </c>
       <c r="L71" s="4"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="6"/>
-      <c r="O71" s="6"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="8"/>
-      <c r="S71" s="8"/>
-      <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
-      <c r="V71" s="9"/>
-      <c r="W71" s="9"/>
-      <c r="X71" s="9"/>
-      <c r="Y71" s="9"/>
-      <c r="Z71" s="9"/>
-      <c r="AA71" s="9"/>
-      <c r="AB71" s="9"/>
-      <c r="AC71" s="9"/>
-      <c r="AD71" s="6"/>
-      <c r="AE71" s="6"/>
-      <c r="AF71" s="6"/>
-      <c r="AG71" s="6"/>
-      <c r="AH71" s="6"/>
-      <c r="AI71" s="6"/>
-      <c r="AJ71" s="6"/>
-      <c r="AK71" s="6"/>
-      <c r="AL71" s="6"/>
-      <c r="AM71" s="6"/>
-      <c r="AN71" s="9"/>
-      <c r="AO71" s="6"/>
+      <c r="M71" s="5">
+        <v>5548.1599999999999</v>
+      </c>
+      <c r="N71" s="6">
+        <v>70</v>
+      </c>
+      <c r="O71" s="6">
+        <v>24</v>
+      </c>
+      <c r="P71" s="7">
+        <v>4.3948529411764712</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>14.254166666666668</v>
+      </c>
+      <c r="R71" s="8">
+        <v>4.2058349999999995</v>
+      </c>
+      <c r="S71" s="8">
+        <v>8</v>
+      </c>
+      <c r="T71" s="9">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="U71" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V71" s="9">
+        <v>0</v>
+      </c>
+      <c r="W71" s="9">
+        <v>0</v>
+      </c>
+      <c r="X71" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="Y71" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="Z71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="9">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="AB71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI71" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP71" s="4">
         <v>58</v>
       </c>
@@ -11837,7 +12542,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>51</v>
@@ -11867,35 +12572,93 @@
         <v>58</v>
       </c>
       <c r="L75" s="4"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
-      <c r="S75" s="8"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="9"/>
-      <c r="AA75" s="9"/>
-      <c r="AB75" s="9"/>
-      <c r="AC75" s="9"/>
-      <c r="AD75" s="6"/>
-      <c r="AE75" s="6"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="6"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="6"/>
-      <c r="AL75" s="6"/>
-      <c r="AM75" s="6"/>
-      <c r="AN75" s="9"/>
-      <c r="AO75" s="6"/>
+      <c r="M75" s="5">
+        <v>5034.3599999999997</v>
+      </c>
+      <c r="N75" s="6">
+        <v>47</v>
+      </c>
+      <c r="O75" s="6">
+        <v>34</v>
+      </c>
+      <c r="P75" s="7">
+        <v>5.6400702127659574</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>22.514705882352942</v>
+      </c>
+      <c r="R75" s="8">
+        <v>9.7730382352941181</v>
+      </c>
+      <c r="S75" s="8">
+        <v>7</v>
+      </c>
+      <c r="T75" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="U75" s="9">
+        <v>0.088235294117647065</v>
+      </c>
+      <c r="V75" s="9">
+        <v>0</v>
+      </c>
+      <c r="W75" s="9">
+        <v>0</v>
+      </c>
+      <c r="X75" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="Y75" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AC75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP75" s="4">
         <v>58</v>
       </c>
@@ -12091,7 +12854,7 @@
         <v>19665</v>
       </c>
       <c r="B77" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C77" s="4">
         <v>51</v>
@@ -12121,35 +12884,93 @@
         <v>58</v>
       </c>
       <c r="L77" s="4"/>
-      <c r="M77" s="5"/>
-      <c r="N77" s="6"/>
-      <c r="O77" s="6"/>
-      <c r="P77" s="7"/>
-      <c r="Q77" s="8"/>
-      <c r="R77" s="8"/>
-      <c r="S77" s="8"/>
-      <c r="T77" s="9"/>
-      <c r="U77" s="9"/>
-      <c r="V77" s="9"/>
-      <c r="W77" s="9"/>
-      <c r="X77" s="9"/>
-      <c r="Y77" s="9"/>
-      <c r="Z77" s="9"/>
-      <c r="AA77" s="9"/>
-      <c r="AB77" s="9"/>
-      <c r="AC77" s="9"/>
-      <c r="AD77" s="6"/>
-      <c r="AE77" s="6"/>
-      <c r="AF77" s="6"/>
-      <c r="AG77" s="6"/>
-      <c r="AH77" s="6"/>
-      <c r="AI77" s="6"/>
-      <c r="AJ77" s="6"/>
-      <c r="AK77" s="6"/>
-      <c r="AL77" s="6"/>
-      <c r="AM77" s="6"/>
-      <c r="AN77" s="9"/>
-      <c r="AO77" s="6"/>
+      <c r="M77" s="5">
+        <v>4900.7600000000002</v>
+      </c>
+      <c r="N77" s="6">
+        <v>47</v>
+      </c>
+      <c r="O77" s="6">
+        <v>40</v>
+      </c>
+      <c r="P77" s="7">
+        <v>2.7290787234042551</v>
+      </c>
+      <c r="Q77" s="8">
+        <v>13.176667499999999</v>
+      </c>
+      <c r="R77" s="8">
+        <v>3.5833333333333335</v>
+      </c>
+      <c r="S77" s="8">
+        <v>7</v>
+      </c>
+      <c r="T77" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="U77" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="V77" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="W77" s="9">
+        <v>0</v>
+      </c>
+      <c r="X77" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="Y77" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="Z77" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="AB77" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE77" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF77" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI77" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP77" s="4">
         <v>58</v>
       </c>
@@ -15706,7 +16527,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -15736,35 +16557,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>3191.8800000000001</v>
+      </c>
+      <c r="N102" s="6">
+        <v>32</v>
+      </c>
+      <c r="O102" s="6">
+        <v>21</v>
+      </c>
+      <c r="P102" s="7">
+        <v>7.0739593750000003</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>33.951585714285713</v>
+      </c>
+      <c r="R102" s="8">
+        <v>23.126315789473683</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0.095238095238000003</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -16431,7 +17310,7 @@
         <v>19727</v>
       </c>
       <c r="B107" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C107" s="4">
         <v>51</v>
@@ -16461,35 +17340,93 @@
         <v>58</v>
       </c>
       <c r="L107" s="4"/>
-      <c r="M107" s="5"/>
-      <c r="N107" s="6"/>
-      <c r="O107" s="6"/>
-      <c r="P107" s="7"/>
-      <c r="Q107" s="8"/>
-      <c r="R107" s="8"/>
-      <c r="S107" s="8"/>
-      <c r="T107" s="9"/>
-      <c r="U107" s="9"/>
-      <c r="V107" s="9"/>
-      <c r="W107" s="9"/>
-      <c r="X107" s="9"/>
-      <c r="Y107" s="9"/>
-      <c r="Z107" s="9"/>
-      <c r="AA107" s="9"/>
-      <c r="AB107" s="9"/>
-      <c r="AC107" s="9"/>
-      <c r="AD107" s="6"/>
-      <c r="AE107" s="6"/>
-      <c r="AF107" s="6"/>
-      <c r="AG107" s="6"/>
-      <c r="AH107" s="6"/>
-      <c r="AI107" s="6"/>
-      <c r="AJ107" s="6"/>
-      <c r="AK107" s="6"/>
-      <c r="AL107" s="6"/>
-      <c r="AM107" s="6"/>
-      <c r="AN107" s="9"/>
-      <c r="AO107" s="6"/>
+      <c r="M107" s="5">
+        <v>2802.1500000000001</v>
+      </c>
+      <c r="N107" s="6">
+        <v>30</v>
+      </c>
+      <c r="O107" s="6">
+        <v>19</v>
+      </c>
+      <c r="P107" s="7">
+        <v>5.1896551724137927</v>
+      </c>
+      <c r="Q107" s="8">
+        <v>18.464036842105266</v>
+      </c>
+      <c r="R107" s="8">
+        <v>5.8359631578947369</v>
+      </c>
+      <c r="S107" s="8">
+        <v>7</v>
+      </c>
+      <c r="T107" s="9">
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="U107" s="9">
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="V107" s="9">
+        <v>0</v>
+      </c>
+      <c r="W107" s="9">
+        <v>0</v>
+      </c>
+      <c r="X107" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB107" s="9">
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="AC107" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD107" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE107" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL107" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN107" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO107" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP107" s="4">
         <v>58</v>
       </c>
@@ -17292,7 +18229,7 @@
         <v>19740</v>
       </c>
       <c r="B114" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C114" s="4">
         <v>51</v>
@@ -17322,35 +18259,93 @@
         <v>58</v>
       </c>
       <c r="L114" s="4"/>
-      <c r="M114" s="5"/>
-      <c r="N114" s="6"/>
-      <c r="O114" s="6"/>
-      <c r="P114" s="7"/>
-      <c r="Q114" s="8"/>
-      <c r="R114" s="8"/>
-      <c r="S114" s="8"/>
-      <c r="T114" s="9"/>
-      <c r="U114" s="9"/>
-      <c r="V114" s="9"/>
-      <c r="W114" s="9"/>
-      <c r="X114" s="9"/>
-      <c r="Y114" s="9"/>
-      <c r="Z114" s="9"/>
-      <c r="AA114" s="9"/>
-      <c r="AB114" s="9"/>
-      <c r="AC114" s="9"/>
-      <c r="AD114" s="6"/>
-      <c r="AE114" s="6"/>
-      <c r="AF114" s="6"/>
-      <c r="AG114" s="6"/>
-      <c r="AH114" s="6"/>
-      <c r="AI114" s="6"/>
-      <c r="AJ114" s="6"/>
-      <c r="AK114" s="6"/>
-      <c r="AL114" s="6"/>
-      <c r="AM114" s="6"/>
-      <c r="AN114" s="9"/>
-      <c r="AO114" s="6"/>
+      <c r="M114" s="5">
+        <v>6052.1199999999999</v>
+      </c>
+      <c r="N114" s="6">
+        <v>46</v>
+      </c>
+      <c r="O114" s="6">
+        <v>41</v>
+      </c>
+      <c r="P114" s="7">
+        <v>4.1572916666666666</v>
+      </c>
+      <c r="Q114" s="8">
+        <v>17.826017073170732</v>
+      </c>
+      <c r="R114" s="8">
+        <v>6.7679487179487179</v>
+      </c>
+      <c r="S114" s="8">
+        <v>8</v>
+      </c>
+      <c r="T114" s="9">
+        <v>0.31707317073170732</v>
+      </c>
+      <c r="U114" s="9">
+        <v>0.36585365853658536</v>
+      </c>
+      <c r="V114" s="9">
+        <v>0</v>
+      </c>
+      <c r="W114" s="9">
+        <v>0</v>
+      </c>
+      <c r="X114" s="9">
+        <v>0.073170731707317069</v>
+      </c>
+      <c r="Y114" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="AA114" s="9">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AB114" s="9">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AC114" s="9">
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="AD114" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE114" s="6">
+        <v>15</v>
+      </c>
+      <c r="AF114" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG114" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH114" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI114" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ114" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK114" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL114" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM114" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN114" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO114" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP114" s="4">
         <v>58</v>
       </c>
@@ -17391,7 +18386,7 @@
         <v>19741</v>
       </c>
       <c r="B115" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C115" s="4">
         <v>51</v>
@@ -17421,35 +18416,93 @@
         <v>58</v>
       </c>
       <c r="L115" s="4"/>
-      <c r="M115" s="5"/>
-      <c r="N115" s="6"/>
-      <c r="O115" s="6"/>
-      <c r="P115" s="7"/>
-      <c r="Q115" s="8"/>
-      <c r="R115" s="8"/>
-      <c r="S115" s="8"/>
-      <c r="T115" s="9"/>
-      <c r="U115" s="9"/>
-      <c r="V115" s="9"/>
-      <c r="W115" s="9"/>
-      <c r="X115" s="9"/>
-      <c r="Y115" s="9"/>
-      <c r="Z115" s="9"/>
-      <c r="AA115" s="9"/>
-      <c r="AB115" s="9"/>
-      <c r="AC115" s="9"/>
-      <c r="AD115" s="6"/>
-      <c r="AE115" s="6"/>
-      <c r="AF115" s="6"/>
-      <c r="AG115" s="6"/>
-      <c r="AH115" s="6"/>
-      <c r="AI115" s="6"/>
-      <c r="AJ115" s="6"/>
-      <c r="AK115" s="6"/>
-      <c r="AL115" s="6"/>
-      <c r="AM115" s="6"/>
-      <c r="AN115" s="9"/>
-      <c r="AO115" s="6"/>
+      <c r="M115" s="5">
+        <v>2944.6999999999998</v>
+      </c>
+      <c r="N115" s="6">
+        <v>34</v>
+      </c>
+      <c r="O115" s="6">
+        <v>28</v>
+      </c>
+      <c r="P115" s="7">
+        <v>7.322857142857143</v>
+      </c>
+      <c r="Q115" s="8">
+        <v>20.891667857142856</v>
+      </c>
+      <c r="R115" s="8">
+        <v>11.591665384615386</v>
+      </c>
+      <c r="S115" s="8">
+        <v>8</v>
+      </c>
+      <c r="T115" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="U115" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="V115" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="W115" s="9">
+        <v>0.035714285714000003</v>
+      </c>
+      <c r="X115" s="9">
+        <v>0.17857142857142858</v>
+      </c>
+      <c r="Y115" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="Z115" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA115" s="9">
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="AB115" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="AC115" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD115" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE115" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF115" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG115" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH115" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI115" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ115" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK115" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL115" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM115" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN115" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO115" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP115" s="4">
         <v>58</v>
       </c>
@@ -18994,7 +20047,7 @@
         <v>19759</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C126" s="4">
         <v>51</v>
@@ -19024,35 +20077,93 @@
         <v>58</v>
       </c>
       <c r="L126" s="4"/>
-      <c r="M126" s="5"/>
-      <c r="N126" s="6"/>
-      <c r="O126" s="6"/>
-      <c r="P126" s="7"/>
-      <c r="Q126" s="8"/>
-      <c r="R126" s="8"/>
-      <c r="S126" s="8"/>
-      <c r="T126" s="9"/>
-      <c r="U126" s="9"/>
-      <c r="V126" s="9"/>
-      <c r="W126" s="9"/>
-      <c r="X126" s="9"/>
-      <c r="Y126" s="9"/>
-      <c r="Z126" s="9"/>
-      <c r="AA126" s="9"/>
-      <c r="AB126" s="9"/>
-      <c r="AC126" s="9"/>
-      <c r="AD126" s="6"/>
-      <c r="AE126" s="6"/>
-      <c r="AF126" s="6"/>
-      <c r="AG126" s="6"/>
-      <c r="AH126" s="6"/>
-      <c r="AI126" s="6"/>
-      <c r="AJ126" s="6"/>
-      <c r="AK126" s="6"/>
-      <c r="AL126" s="6"/>
-      <c r="AM126" s="6"/>
-      <c r="AN126" s="9"/>
-      <c r="AO126" s="6"/>
+      <c r="M126" s="5">
+        <v>2929.0599999999999</v>
+      </c>
+      <c r="N126" s="6">
+        <v>35</v>
+      </c>
+      <c r="O126" s="6">
+        <v>30</v>
+      </c>
+      <c r="P126" s="7">
+        <v>7.3157142857142858</v>
+      </c>
+      <c r="Q126" s="8">
+        <v>28.340231034482759</v>
+      </c>
+      <c r="R126" s="8">
+        <v>15.228571428571428</v>
+      </c>
+      <c r="S126" s="8">
+        <v>7</v>
+      </c>
+      <c r="T126" s="9">
+        <v>0.10344827586206896</v>
+      </c>
+      <c r="U126" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="V126" s="9">
+        <v>0</v>
+      </c>
+      <c r="W126" s="9">
+        <v>0</v>
+      </c>
+      <c r="X126" s="9">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="Y126" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z126" s="9">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="AA126" s="9">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="AB126" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AC126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD126" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE126" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH126" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ126" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK126" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL126" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO126" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP126" s="4">
         <v>58</v>
       </c>
@@ -20506,7 +21617,7 @@
         <v>19785</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C136" s="4">
         <v>51</v>
@@ -20536,35 +21647,93 @@
         <v>58</v>
       </c>
       <c r="L136" s="4"/>
-      <c r="M136" s="5"/>
-      <c r="N136" s="6"/>
-      <c r="O136" s="6"/>
-      <c r="P136" s="7"/>
-      <c r="Q136" s="8"/>
-      <c r="R136" s="8"/>
-      <c r="S136" s="8"/>
-      <c r="T136" s="9"/>
-      <c r="U136" s="9"/>
-      <c r="V136" s="9"/>
-      <c r="W136" s="9"/>
-      <c r="X136" s="9"/>
-      <c r="Y136" s="9"/>
-      <c r="Z136" s="9"/>
-      <c r="AA136" s="9"/>
-      <c r="AB136" s="9"/>
-      <c r="AC136" s="9"/>
-      <c r="AD136" s="6"/>
-      <c r="AE136" s="6"/>
-      <c r="AF136" s="6"/>
-      <c r="AG136" s="6"/>
-      <c r="AH136" s="6"/>
-      <c r="AI136" s="6"/>
-      <c r="AJ136" s="6"/>
-      <c r="AK136" s="6"/>
-      <c r="AL136" s="6"/>
-      <c r="AM136" s="6"/>
-      <c r="AN136" s="9"/>
-      <c r="AO136" s="6"/>
+      <c r="M136" s="5">
+        <v>3496.3099999999999</v>
+      </c>
+      <c r="N136" s="6">
+        <v>35</v>
+      </c>
+      <c r="O136" s="6">
+        <v>27</v>
+      </c>
+      <c r="P136" s="7">
+        <v>10.45965</v>
+      </c>
+      <c r="Q136" s="8">
+        <v>26.290122222222223</v>
+      </c>
+      <c r="R136" s="8">
+        <v>7.5749999999999993</v>
+      </c>
+      <c r="S136" s="8">
+        <v>7</v>
+      </c>
+      <c r="T136" s="9">
+        <v>0.14814814814814814</v>
+      </c>
+      <c r="U136" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="V136" s="9">
+        <v>0</v>
+      </c>
+      <c r="W136" s="9">
+        <v>0</v>
+      </c>
+      <c r="X136" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y136" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="9">
+        <v>0.14814814814814814</v>
+      </c>
+      <c r="AB136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC136" s="9">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="AD136" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE136" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK136" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM136" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO136" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP136" s="4">
         <v>58</v>
       </c>
@@ -22266,7 +23435,7 @@
         <v>19809</v>
       </c>
       <c r="B148" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C148" s="4">
         <v>51</v>
@@ -22296,35 +23465,93 @@
         <v>58</v>
       </c>
       <c r="L148" s="4"/>
-      <c r="M148" s="5"/>
-      <c r="N148" s="6"/>
-      <c r="O148" s="6"/>
-      <c r="P148" s="7"/>
-      <c r="Q148" s="8"/>
-      <c r="R148" s="8"/>
-      <c r="S148" s="8"/>
-      <c r="T148" s="9"/>
-      <c r="U148" s="9"/>
-      <c r="V148" s="9"/>
-      <c r="W148" s="9"/>
-      <c r="X148" s="9"/>
-      <c r="Y148" s="9"/>
-      <c r="Z148" s="9"/>
-      <c r="AA148" s="9"/>
-      <c r="AB148" s="9"/>
-      <c r="AC148" s="9"/>
-      <c r="AD148" s="6"/>
-      <c r="AE148" s="6"/>
-      <c r="AF148" s="6"/>
-      <c r="AG148" s="6"/>
-      <c r="AH148" s="6"/>
-      <c r="AI148" s="6"/>
-      <c r="AJ148" s="6"/>
-      <c r="AK148" s="6"/>
-      <c r="AL148" s="6"/>
-      <c r="AM148" s="6"/>
-      <c r="AN148" s="9"/>
-      <c r="AO148" s="6"/>
+      <c r="M148" s="5">
+        <v>9686.0799999999999</v>
+      </c>
+      <c r="N148" s="6">
+        <v>135</v>
+      </c>
+      <c r="O148" s="6">
+        <v>122</v>
+      </c>
+      <c r="P148" s="7">
+        <v>12.711851851851851</v>
+      </c>
+      <c r="Q148" s="8">
+        <v>32.542486065573769</v>
+      </c>
+      <c r="R148" s="8">
+        <v>14.733823529411763</v>
+      </c>
+      <c r="S148" s="8">
+        <v>8</v>
+      </c>
+      <c r="T148" s="9">
+        <v>0.11475409836065574</v>
+      </c>
+      <c r="U148" s="9">
+        <v>0.71311475409836067</v>
+      </c>
+      <c r="V148" s="9">
+        <v>0</v>
+      </c>
+      <c r="W148" s="9">
+        <v>0</v>
+      </c>
+      <c r="X148" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y148" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z148" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA148" s="9">
+        <v>0.1721311475409836</v>
+      </c>
+      <c r="AB148" s="9">
+        <v>0.05737704918032787</v>
+      </c>
+      <c r="AC148" s="9">
+        <v>0.60655737704918034</v>
+      </c>
+      <c r="AD148" s="6">
+        <v>102</v>
+      </c>
+      <c r="AE148" s="6">
+        <v>87</v>
+      </c>
+      <c r="AF148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK148" s="6">
+        <v>21</v>
+      </c>
+      <c r="AL148" s="6">
+        <v>7</v>
+      </c>
+      <c r="AM148" s="6">
+        <v>74</v>
+      </c>
+      <c r="AN148" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO148" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP148" s="4">
         <v>58</v>
       </c>
@@ -22520,7 +23747,7 @@
         <v>19820</v>
       </c>
       <c r="B150" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C150" s="4">
         <v>51</v>
@@ -22550,35 +23777,93 @@
         <v>58</v>
       </c>
       <c r="L150" s="4"/>
-      <c r="M150" s="5"/>
-      <c r="N150" s="6"/>
-      <c r="O150" s="6"/>
-      <c r="P150" s="7"/>
-      <c r="Q150" s="8"/>
-      <c r="R150" s="8"/>
-      <c r="S150" s="8"/>
-      <c r="T150" s="9"/>
-      <c r="U150" s="9"/>
-      <c r="V150" s="9"/>
-      <c r="W150" s="9"/>
-      <c r="X150" s="9"/>
-      <c r="Y150" s="9"/>
-      <c r="Z150" s="9"/>
-      <c r="AA150" s="9"/>
-      <c r="AB150" s="9"/>
-      <c r="AC150" s="9"/>
-      <c r="AD150" s="6"/>
-      <c r="AE150" s="6"/>
-      <c r="AF150" s="6"/>
-      <c r="AG150" s="6"/>
-      <c r="AH150" s="6"/>
-      <c r="AI150" s="6"/>
-      <c r="AJ150" s="6"/>
-      <c r="AK150" s="6"/>
-      <c r="AL150" s="6"/>
-      <c r="AM150" s="6"/>
-      <c r="AN150" s="9"/>
-      <c r="AO150" s="6"/>
+      <c r="M150" s="5">
+        <v>2025.05</v>
+      </c>
+      <c r="N150" s="6">
+        <v>23</v>
+      </c>
+      <c r="O150" s="6">
+        <v>20</v>
+      </c>
+      <c r="P150" s="7">
+        <v>2.7898565217391309</v>
+      </c>
+      <c r="Q150" s="8">
+        <v>14.1625</v>
+      </c>
+      <c r="R150" s="8">
+        <v>4.8263157894736848</v>
+      </c>
+      <c r="S150" s="8">
+        <v>7</v>
+      </c>
+      <c r="T150" s="9">
+        <v>0.65000000000000002</v>
+      </c>
+      <c r="U150" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="V150" s="9">
+        <v>0</v>
+      </c>
+      <c r="W150" s="9">
+        <v>0</v>
+      </c>
+      <c r="X150" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="Y150" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Z150" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA150" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AB150" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC150" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD150" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE150" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF150" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG150" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH150" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI150" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ150" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK150" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL150" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM150" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN150" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO150" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP150" s="4">
         <v>58</v>
       </c>
@@ -24734,7 +26019,7 @@
         <v>19879</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>51</v>
@@ -24764,35 +26049,93 @@
         <v>58</v>
       </c>
       <c r="L166" s="4"/>
-      <c r="M166" s="5"/>
-      <c r="N166" s="6"/>
-      <c r="O166" s="6"/>
-      <c r="P166" s="7"/>
-      <c r="Q166" s="8"/>
-      <c r="R166" s="8"/>
-      <c r="S166" s="8"/>
-      <c r="T166" s="9"/>
-      <c r="U166" s="9"/>
-      <c r="V166" s="9"/>
-      <c r="W166" s="9"/>
-      <c r="X166" s="9"/>
-      <c r="Y166" s="9"/>
-      <c r="Z166" s="9"/>
-      <c r="AA166" s="9"/>
-      <c r="AB166" s="9"/>
-      <c r="AC166" s="9"/>
-      <c r="AD166" s="6"/>
-      <c r="AE166" s="6"/>
-      <c r="AF166" s="6"/>
-      <c r="AG166" s="6"/>
-      <c r="AH166" s="6"/>
-      <c r="AI166" s="6"/>
-      <c r="AJ166" s="6"/>
-      <c r="AK166" s="6"/>
-      <c r="AL166" s="6"/>
-      <c r="AM166" s="6"/>
-      <c r="AN166" s="9"/>
-      <c r="AO166" s="6"/>
+      <c r="M166" s="5">
+        <v>2847.8000000000002</v>
+      </c>
+      <c r="N166" s="6">
+        <v>26</v>
+      </c>
+      <c r="O166" s="6">
+        <v>19</v>
+      </c>
+      <c r="P166" s="7">
+        <v>3.1623444444444448</v>
+      </c>
+      <c r="Q166" s="8">
+        <v>17.605263157894736</v>
+      </c>
+      <c r="R166" s="8">
+        <v>7.5061421052631587</v>
+      </c>
+      <c r="S166" s="8">
+        <v>7</v>
+      </c>
+      <c r="T166" s="9">
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="U166" s="9">
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="V166" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="W166" s="9">
+        <v>0</v>
+      </c>
+      <c r="X166" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y166" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z166" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA166" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB166" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC166" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="AD166" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE166" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF166" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG166" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH166" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI166" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ166" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK166" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL166" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM166" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN166" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO166" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP166" s="4">
         <v>58</v>
       </c>
@@ -26087,7 +27430,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>51</v>
@@ -26117,35 +27460,93 @@
         <v>58</v>
       </c>
       <c r="L175" s="4"/>
-      <c r="M175" s="5"/>
-      <c r="N175" s="6"/>
-      <c r="O175" s="6"/>
-      <c r="P175" s="7"/>
-      <c r="Q175" s="8"/>
-      <c r="R175" s="8"/>
-      <c r="S175" s="8"/>
-      <c r="T175" s="9"/>
-      <c r="U175" s="9"/>
-      <c r="V175" s="9"/>
-      <c r="W175" s="9"/>
-      <c r="X175" s="9"/>
-      <c r="Y175" s="9"/>
-      <c r="Z175" s="9"/>
-      <c r="AA175" s="9"/>
-      <c r="AB175" s="9"/>
-      <c r="AC175" s="9"/>
-      <c r="AD175" s="6"/>
-      <c r="AE175" s="6"/>
-      <c r="AF175" s="6"/>
-      <c r="AG175" s="6"/>
-      <c r="AH175" s="6"/>
-      <c r="AI175" s="6"/>
-      <c r="AJ175" s="6"/>
-      <c r="AK175" s="6"/>
-      <c r="AL175" s="6"/>
-      <c r="AM175" s="6"/>
-      <c r="AN175" s="9"/>
-      <c r="AO175" s="6"/>
+      <c r="M175" s="5">
+        <v>2441.6900000000001</v>
+      </c>
+      <c r="N175" s="6">
+        <v>32</v>
+      </c>
+      <c r="O175" s="6">
+        <v>15</v>
+      </c>
+      <c r="P175" s="7">
+        <v>8.3442517241379317</v>
+      </c>
+      <c r="Q175" s="8">
+        <v>20.94111333333333</v>
+      </c>
+      <c r="R175" s="8">
+        <v>5.2644466666666672</v>
+      </c>
+      <c r="S175" s="8">
+        <v>7</v>
+      </c>
+      <c r="T175" s="9">
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="U175" s="9">
+        <v>0</v>
+      </c>
+      <c r="V175" s="9">
+        <v>0</v>
+      </c>
+      <c r="W175" s="9">
+        <v>0</v>
+      </c>
+      <c r="X175" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y175" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO175" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP175" s="4">
         <v>58</v>
       </c>
@@ -26808,7 +28209,7 @@
         <v>19908</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C180" s="4">
         <v>51</v>
@@ -26838,35 +28239,93 @@
         <v>58</v>
       </c>
       <c r="L180" s="4"/>
-      <c r="M180" s="5"/>
-      <c r="N180" s="6"/>
-      <c r="O180" s="6"/>
-      <c r="P180" s="7"/>
-      <c r="Q180" s="8"/>
-      <c r="R180" s="8"/>
-      <c r="S180" s="8"/>
-      <c r="T180" s="9"/>
-      <c r="U180" s="9"/>
-      <c r="V180" s="9"/>
-      <c r="W180" s="9"/>
-      <c r="X180" s="9"/>
-      <c r="Y180" s="9"/>
-      <c r="Z180" s="9"/>
-      <c r="AA180" s="9"/>
-      <c r="AB180" s="9"/>
-      <c r="AC180" s="9"/>
-      <c r="AD180" s="6"/>
-      <c r="AE180" s="6"/>
-      <c r="AF180" s="6"/>
-      <c r="AG180" s="6"/>
-      <c r="AH180" s="6"/>
-      <c r="AI180" s="6"/>
-      <c r="AJ180" s="6"/>
-      <c r="AK180" s="6"/>
-      <c r="AL180" s="6"/>
-      <c r="AM180" s="6"/>
-      <c r="AN180" s="9"/>
-      <c r="AO180" s="6"/>
+      <c r="M180" s="5">
+        <v>2521.52</v>
+      </c>
+      <c r="N180" s="6">
+        <v>33</v>
+      </c>
+      <c r="O180" s="6">
+        <v>14</v>
+      </c>
+      <c r="P180" s="7">
+        <v>8.0713531249999999</v>
+      </c>
+      <c r="Q180" s="8">
+        <v>39.346428571428575</v>
+      </c>
+      <c r="R180" s="8">
+        <v>22.671428571428571</v>
+      </c>
+      <c r="S180" s="8">
+        <v>8</v>
+      </c>
+      <c r="T180" s="9">
+        <v>0</v>
+      </c>
+      <c r="U180" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="V180" s="9">
+        <v>0</v>
+      </c>
+      <c r="W180" s="9">
+        <v>0</v>
+      </c>
+      <c r="X180" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y180" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC180" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AD180" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE180" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM180" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO180" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP180" s="4">
         <v>58</v>
       </c>
@@ -26907,7 +28366,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>51</v>
@@ -26937,35 +28396,93 @@
         <v>58</v>
       </c>
       <c r="L181" s="4"/>
-      <c r="M181" s="5"/>
-      <c r="N181" s="6"/>
-      <c r="O181" s="6"/>
-      <c r="P181" s="7"/>
-      <c r="Q181" s="8"/>
-      <c r="R181" s="8"/>
-      <c r="S181" s="8"/>
-      <c r="T181" s="9"/>
-      <c r="U181" s="9"/>
-      <c r="V181" s="9"/>
-      <c r="W181" s="9"/>
-      <c r="X181" s="9"/>
-      <c r="Y181" s="9"/>
-      <c r="Z181" s="9"/>
-      <c r="AA181" s="9"/>
-      <c r="AB181" s="9"/>
-      <c r="AC181" s="9"/>
-      <c r="AD181" s="6"/>
-      <c r="AE181" s="6"/>
-      <c r="AF181" s="6"/>
-      <c r="AG181" s="6"/>
-      <c r="AH181" s="6"/>
-      <c r="AI181" s="6"/>
-      <c r="AJ181" s="6"/>
-      <c r="AK181" s="6"/>
-      <c r="AL181" s="6"/>
-      <c r="AM181" s="6"/>
-      <c r="AN181" s="9"/>
-      <c r="AO181" s="6"/>
+      <c r="M181" s="5">
+        <v>2743.6999999999998</v>
+      </c>
+      <c r="N181" s="6">
+        <v>30</v>
+      </c>
+      <c r="O181" s="6">
+        <v>21</v>
+      </c>
+      <c r="P181" s="7">
+        <v>4.0194433333333333</v>
+      </c>
+      <c r="Q181" s="8">
+        <v>12.588095238095239</v>
+      </c>
+      <c r="R181" s="8">
+        <v>2.552775</v>
+      </c>
+      <c r="S181" s="8">
+        <v>8</v>
+      </c>
+      <c r="T181" s="9">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="U181" s="9">
+        <v>0.47619047619047616</v>
+      </c>
+      <c r="V181" s="9">
+        <v>0</v>
+      </c>
+      <c r="W181" s="9">
+        <v>0</v>
+      </c>
+      <c r="X181" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="Y181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="9">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="AB181" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="AC181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD181" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH181" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK181" s="6">
+        <v>9</v>
+      </c>
+      <c r="AL181" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO181" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP181" s="4">
         <v>58</v>
       </c>
@@ -27675,7 +29192,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>51</v>
@@ -27705,35 +29222,93 @@
         <v>58</v>
       </c>
       <c r="L187" s="4"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="6"/>
-      <c r="O187" s="6"/>
-      <c r="P187" s="7"/>
-      <c r="Q187" s="8"/>
-      <c r="R187" s="8"/>
-      <c r="S187" s="8"/>
-      <c r="T187" s="9"/>
-      <c r="U187" s="9"/>
-      <c r="V187" s="9"/>
-      <c r="W187" s="9"/>
-      <c r="X187" s="9"/>
-      <c r="Y187" s="9"/>
-      <c r="Z187" s="9"/>
-      <c r="AA187" s="9"/>
-      <c r="AB187" s="9"/>
-      <c r="AC187" s="9"/>
-      <c r="AD187" s="6"/>
-      <c r="AE187" s="6"/>
-      <c r="AF187" s="6"/>
-      <c r="AG187" s="6"/>
-      <c r="AH187" s="6"/>
-      <c r="AI187" s="6"/>
-      <c r="AJ187" s="6"/>
-      <c r="AK187" s="6"/>
-      <c r="AL187" s="6"/>
-      <c r="AM187" s="6"/>
-      <c r="AN187" s="9"/>
-      <c r="AO187" s="6"/>
+      <c r="M187" s="5">
+        <v>1697.9000000000001</v>
+      </c>
+      <c r="N187" s="6">
+        <v>24</v>
+      </c>
+      <c r="O187" s="6">
+        <v>12</v>
+      </c>
+      <c r="P187" s="7">
+        <v>7.6868041666666675</v>
+      </c>
+      <c r="Q187" s="8">
+        <v>31.394441666666665</v>
+      </c>
+      <c r="R187" s="8">
+        <v>16.620833333333334</v>
+      </c>
+      <c r="S187" s="8">
+        <v>7</v>
+      </c>
+      <c r="T187" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="U187" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="V187" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="W187" s="9">
+        <v>0</v>
+      </c>
+      <c r="X187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF187" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO187" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP187" s="4">
         <v>58</v>
       </c>
@@ -27931,7 +29506,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>51</v>
@@ -27961,35 +29536,93 @@
         <v>58</v>
       </c>
       <c r="L189" s="4"/>
-      <c r="M189" s="5"/>
-      <c r="N189" s="6"/>
-      <c r="O189" s="6"/>
-      <c r="P189" s="7"/>
-      <c r="Q189" s="8"/>
-      <c r="R189" s="8"/>
-      <c r="S189" s="8"/>
-      <c r="T189" s="9"/>
-      <c r="U189" s="9"/>
-      <c r="V189" s="9"/>
-      <c r="W189" s="9"/>
-      <c r="X189" s="9"/>
-      <c r="Y189" s="9"/>
-      <c r="Z189" s="9"/>
-      <c r="AA189" s="9"/>
-      <c r="AB189" s="9"/>
-      <c r="AC189" s="9"/>
-      <c r="AD189" s="6"/>
-      <c r="AE189" s="6"/>
-      <c r="AF189" s="6"/>
-      <c r="AG189" s="6"/>
-      <c r="AH189" s="6"/>
-      <c r="AI189" s="6"/>
-      <c r="AJ189" s="6"/>
-      <c r="AK189" s="6"/>
-      <c r="AL189" s="6"/>
-      <c r="AM189" s="6"/>
-      <c r="AN189" s="9"/>
-      <c r="AO189" s="6"/>
+      <c r="M189" s="5">
+        <v>4451.6300000000001</v>
+      </c>
+      <c r="N189" s="6">
+        <v>67</v>
+      </c>
+      <c r="O189" s="6">
+        <v>64</v>
+      </c>
+      <c r="P189" s="7">
+        <v>5.674754411764706</v>
+      </c>
+      <c r="Q189" s="8">
+        <v>22.805468749999999</v>
+      </c>
+      <c r="R189" s="8">
+        <v>10.358995238095238</v>
+      </c>
+      <c r="S189" s="8">
+        <v>7</v>
+      </c>
+      <c r="T189" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="U189" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="V189" s="9">
+        <v>0.015625</v>
+      </c>
+      <c r="W189" s="9">
+        <v>0</v>
+      </c>
+      <c r="X189" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="Y189" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="9">
+        <v>0.015625</v>
+      </c>
+      <c r="AB189" s="9">
+        <v>0.015625</v>
+      </c>
+      <c r="AC189" s="9">
+        <v>0.1875</v>
+      </c>
+      <c r="AD189" s="6">
+        <v>17</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH189" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM189" s="6">
+        <v>12</v>
+      </c>
+      <c r="AN189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO189" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP189" s="4">
         <v>58</v>
       </c>
@@ -28030,7 +29663,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>51</v>
@@ -28060,35 +29693,93 @@
         <v>58</v>
       </c>
       <c r="L190" s="4"/>
-      <c r="M190" s="5"/>
-      <c r="N190" s="6"/>
-      <c r="O190" s="6"/>
-      <c r="P190" s="7"/>
-      <c r="Q190" s="8"/>
-      <c r="R190" s="8"/>
-      <c r="S190" s="8"/>
-      <c r="T190" s="9"/>
-      <c r="U190" s="9"/>
-      <c r="V190" s="9"/>
-      <c r="W190" s="9"/>
-      <c r="X190" s="9"/>
-      <c r="Y190" s="9"/>
-      <c r="Z190" s="9"/>
-      <c r="AA190" s="9"/>
-      <c r="AB190" s="9"/>
-      <c r="AC190" s="9"/>
-      <c r="AD190" s="6"/>
-      <c r="AE190" s="6"/>
-      <c r="AF190" s="6"/>
-      <c r="AG190" s="6"/>
-      <c r="AH190" s="6"/>
-      <c r="AI190" s="6"/>
-      <c r="AJ190" s="6"/>
-      <c r="AK190" s="6"/>
-      <c r="AL190" s="6"/>
-      <c r="AM190" s="6"/>
-      <c r="AN190" s="9"/>
-      <c r="AO190" s="6"/>
+      <c r="M190" s="5">
+        <v>3769.0700000000002</v>
+      </c>
+      <c r="N190" s="6">
+        <v>42</v>
+      </c>
+      <c r="O190" s="6">
+        <v>20</v>
+      </c>
+      <c r="P190" s="7">
+        <v>3.8424595238095236</v>
+      </c>
+      <c r="Q190" s="8">
+        <v>19.588594736842104</v>
+      </c>
+      <c r="R190" s="8">
+        <v>8.4263157894736835</v>
+      </c>
+      <c r="S190" s="8">
+        <v>7</v>
+      </c>
+      <c r="T190" s="9">
+        <v>0.26315789473684209</v>
+      </c>
+      <c r="U190" s="9">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="V190" s="9">
+        <v>0</v>
+      </c>
+      <c r="W190" s="9">
+        <v>0</v>
+      </c>
+      <c r="X190" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y190" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z190" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AA190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB190" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AC190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD190" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL190" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO190" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP190" s="4">
         <v>58</v>
       </c>
@@ -28791,7 +30482,9 @@
       <c r="N195" s="6">
         <v>56</v>
       </c>
-      <c r="O195" s="6"/>
+      <c r="O195" s="6">
+        <v>39</v>
+      </c>
       <c r="P195" s="7">
         <v>4.9996725490196079</v>
       </c>
@@ -28801,31 +30494,75 @@
       <c r="R195" s="8">
         <v>10.942735897435897</v>
       </c>
-      <c r="S195" s="8"/>
+      <c r="S195" s="8">
+        <v>7</v>
+      </c>
       <c r="T195" s="9">
         <v>0.12820512820512819</v>
       </c>
-      <c r="U195" s="9"/>
-      <c r="V195" s="9"/>
-      <c r="W195" s="9"/>
-      <c r="X195" s="9"/>
-      <c r="Y195" s="9"/>
-      <c r="Z195" s="9"/>
-      <c r="AA195" s="9"/>
-      <c r="AB195" s="9"/>
-      <c r="AC195" s="9"/>
-      <c r="AD195" s="6"/>
-      <c r="AE195" s="6"/>
-      <c r="AF195" s="6"/>
-      <c r="AG195" s="6"/>
-      <c r="AH195" s="6"/>
-      <c r="AI195" s="6"/>
-      <c r="AJ195" s="6"/>
-      <c r="AK195" s="6"/>
-      <c r="AL195" s="6"/>
-      <c r="AM195" s="6"/>
-      <c r="AN195" s="9"/>
-      <c r="AO195" s="6"/>
+      <c r="U195" s="9">
+        <v>0</v>
+      </c>
+      <c r="V195" s="9">
+        <v>0</v>
+      </c>
+      <c r="W195" s="9">
+        <v>0</v>
+      </c>
+      <c r="X195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO195" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP195" s="4">
         <v>58</v>
       </c>
@@ -29337,7 +31074,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>51</v>
@@ -29367,35 +31104,93 @@
         <v>58</v>
       </c>
       <c r="L199" s="4"/>
-      <c r="M199" s="5"/>
-      <c r="N199" s="6"/>
-      <c r="O199" s="6"/>
-      <c r="P199" s="7"/>
-      <c r="Q199" s="8"/>
-      <c r="R199" s="8"/>
-      <c r="S199" s="8"/>
-      <c r="T199" s="9"/>
-      <c r="U199" s="9"/>
-      <c r="V199" s="9"/>
-      <c r="W199" s="9"/>
-      <c r="X199" s="9"/>
-      <c r="Y199" s="9"/>
-      <c r="Z199" s="9"/>
-      <c r="AA199" s="9"/>
-      <c r="AB199" s="9"/>
-      <c r="AC199" s="9"/>
-      <c r="AD199" s="6"/>
-      <c r="AE199" s="6"/>
-      <c r="AF199" s="6"/>
-      <c r="AG199" s="6"/>
-      <c r="AH199" s="6"/>
-      <c r="AI199" s="6"/>
-      <c r="AJ199" s="6"/>
-      <c r="AK199" s="6"/>
-      <c r="AL199" s="6"/>
-      <c r="AM199" s="6"/>
-      <c r="AN199" s="9"/>
-      <c r="AO199" s="6"/>
+      <c r="M199" s="5">
+        <v>3253.1300000000001</v>
+      </c>
+      <c r="N199" s="6">
+        <v>35</v>
+      </c>
+      <c r="O199" s="6">
+        <v>20</v>
+      </c>
+      <c r="P199" s="7">
+        <v>5.0606472222222223</v>
+      </c>
+      <c r="Q199" s="8">
+        <v>25.854165000000002</v>
+      </c>
+      <c r="R199" s="8">
+        <v>13.330834999999999</v>
+      </c>
+      <c r="S199" s="8">
+        <v>7</v>
+      </c>
+      <c r="T199" s="9">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="U199" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="V199" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="W199" s="9">
+        <v>0</v>
+      </c>
+      <c r="X199" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Y199" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB199" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AC199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD199" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF199" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH199" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL199" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO199" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP199" s="4">
         <v>58</v>
       </c>
@@ -29436,7 +31231,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>51</v>
@@ -29466,35 +31261,93 @@
         <v>58</v>
       </c>
       <c r="L200" s="4"/>
-      <c r="M200" s="5"/>
-      <c r="N200" s="6"/>
-      <c r="O200" s="6"/>
-      <c r="P200" s="7"/>
-      <c r="Q200" s="8"/>
-      <c r="R200" s="8"/>
-      <c r="S200" s="8"/>
-      <c r="T200" s="9"/>
-      <c r="U200" s="9"/>
-      <c r="V200" s="9"/>
-      <c r="W200" s="9"/>
-      <c r="X200" s="9"/>
-      <c r="Y200" s="9"/>
-      <c r="Z200" s="9"/>
-      <c r="AA200" s="9"/>
-      <c r="AB200" s="9"/>
-      <c r="AC200" s="9"/>
-      <c r="AD200" s="6"/>
-      <c r="AE200" s="6"/>
-      <c r="AF200" s="6"/>
-      <c r="AG200" s="6"/>
-      <c r="AH200" s="6"/>
-      <c r="AI200" s="6"/>
-      <c r="AJ200" s="6"/>
-      <c r="AK200" s="6"/>
-      <c r="AL200" s="6"/>
-      <c r="AM200" s="6"/>
-      <c r="AN200" s="9"/>
-      <c r="AO200" s="6"/>
+      <c r="M200" s="5">
+        <v>1337.98</v>
+      </c>
+      <c r="N200" s="6">
+        <v>18</v>
+      </c>
+      <c r="O200" s="6">
+        <v>12</v>
+      </c>
+      <c r="P200" s="7">
+        <v>7.3777777777777782</v>
+      </c>
+      <c r="Q200" s="8">
+        <v>17.379166666666666</v>
+      </c>
+      <c r="R200" s="8">
+        <v>2.3180583333333336</v>
+      </c>
+      <c r="S200" s="8">
+        <v>7</v>
+      </c>
+      <c r="T200" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U200" s="9">
+        <v>0</v>
+      </c>
+      <c r="V200" s="9">
+        <v>0</v>
+      </c>
+      <c r="W200" s="9">
+        <v>0</v>
+      </c>
+      <c r="X200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO200" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP200" s="4">
         <v>58</v>
       </c>
@@ -30047,7 +31900,7 @@
         <v>19959</v>
       </c>
       <c r="B205" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C205" s="4">
         <v>51</v>
@@ -30077,35 +31930,93 @@
         <v>58</v>
       </c>
       <c r="L205" s="4"/>
-      <c r="M205" s="5"/>
-      <c r="N205" s="6"/>
-      <c r="O205" s="6"/>
-      <c r="P205" s="7"/>
-      <c r="Q205" s="8"/>
-      <c r="R205" s="8"/>
-      <c r="S205" s="8"/>
-      <c r="T205" s="9"/>
-      <c r="U205" s="9"/>
-      <c r="V205" s="9"/>
-      <c r="W205" s="9"/>
-      <c r="X205" s="9"/>
-      <c r="Y205" s="9"/>
-      <c r="Z205" s="9"/>
-      <c r="AA205" s="9"/>
-      <c r="AB205" s="9"/>
-      <c r="AC205" s="9"/>
-      <c r="AD205" s="6"/>
-      <c r="AE205" s="6"/>
-      <c r="AF205" s="6"/>
-      <c r="AG205" s="6"/>
-      <c r="AH205" s="6"/>
-      <c r="AI205" s="6"/>
-      <c r="AJ205" s="6"/>
-      <c r="AK205" s="6"/>
-      <c r="AL205" s="6"/>
-      <c r="AM205" s="6"/>
-      <c r="AN205" s="9"/>
-      <c r="AO205" s="6"/>
+      <c r="M205" s="5">
+        <v>3019.6799999999998</v>
+      </c>
+      <c r="N205" s="6">
+        <v>37</v>
+      </c>
+      <c r="O205" s="6">
+        <v>13</v>
+      </c>
+      <c r="P205" s="7">
+        <v>5.4226861111111111</v>
+      </c>
+      <c r="Q205" s="8">
+        <v>13.39743846153846</v>
+      </c>
+      <c r="R205" s="8">
+        <v>1.5954545454545455</v>
+      </c>
+      <c r="S205" s="8">
+        <v>7</v>
+      </c>
+      <c r="T205" s="9">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="U205" s="9">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="V205" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="W205" s="9">
+        <v>0</v>
+      </c>
+      <c r="X205" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y205" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA205" s="9">
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="AB205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD205" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE205" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF205" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK205" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO205" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP205" s="4">
         <v>58</v>
       </c>
@@ -31366,7 +33277,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>51</v>
@@ -31396,35 +33307,93 @@
         <v>58</v>
       </c>
       <c r="L216" s="4"/>
-      <c r="M216" s="5"/>
-      <c r="N216" s="6"/>
-      <c r="O216" s="6"/>
-      <c r="P216" s="7"/>
-      <c r="Q216" s="8"/>
-      <c r="R216" s="8"/>
-      <c r="S216" s="8"/>
-      <c r="T216" s="9"/>
-      <c r="U216" s="9"/>
-      <c r="V216" s="9"/>
-      <c r="W216" s="9"/>
-      <c r="X216" s="9"/>
-      <c r="Y216" s="9"/>
-      <c r="Z216" s="9"/>
-      <c r="AA216" s="9"/>
-      <c r="AB216" s="9"/>
-      <c r="AC216" s="9"/>
-      <c r="AD216" s="6"/>
-      <c r="AE216" s="6"/>
-      <c r="AF216" s="6"/>
-      <c r="AG216" s="6"/>
-      <c r="AH216" s="6"/>
-      <c r="AI216" s="6"/>
-      <c r="AJ216" s="6"/>
-      <c r="AK216" s="6"/>
-      <c r="AL216" s="6"/>
-      <c r="AM216" s="6"/>
-      <c r="AN216" s="9"/>
-      <c r="AO216" s="6"/>
+      <c r="M216" s="5">
+        <v>6616.6999999999998</v>
+      </c>
+      <c r="N216" s="6">
+        <v>80</v>
+      </c>
+      <c r="O216" s="6">
+        <v>55</v>
+      </c>
+      <c r="P216" s="7">
+        <v>10.27818888888889</v>
+      </c>
+      <c r="Q216" s="8">
+        <v>30.151514545454546</v>
+      </c>
+      <c r="R216" s="8">
+        <v>12.456060000000001</v>
+      </c>
+      <c r="S216" s="8">
+        <v>7</v>
+      </c>
+      <c r="T216" s="9">
+        <v>0.10909090909090909</v>
+      </c>
+      <c r="U216" s="9">
+        <v>0.072727272727272724</v>
+      </c>
+      <c r="V216" s="9">
+        <v>0</v>
+      </c>
+      <c r="W216" s="9">
+        <v>0</v>
+      </c>
+      <c r="X216" s="9">
+        <v>0.018181818181818181</v>
+      </c>
+      <c r="Y216" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB216" s="9">
+        <v>0.054545454545454543</v>
+      </c>
+      <c r="AC216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD216" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE216" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL216" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO216" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP216" s="4">
         <v>58</v>
       </c>
@@ -31517,52 +33486,52 @@
         <v>322</v>
       </c>
       <c t="s" r="Z217" s="11">
+        <v>320</v>
+      </c>
+      <c t="s" r="AA217" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AA217" s="11">
+      <c t="s" r="AB217" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AB217" s="11">
+      <c t="s" r="AC217" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AC217" s="11">
+      <c t="s" r="AD217" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AD217" s="11">
+      <c t="s" r="AE217" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AE217" s="11">
+      <c t="s" r="AF217" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AF217" s="11">
+      <c t="s" r="AG217" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AG217" s="11">
+      <c t="s" r="AH217" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AH217" s="11">
+      <c t="s" r="AI217" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AI217" s="11">
+      <c t="s" r="AJ217" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AJ217" s="11">
+      <c t="s" r="AK217" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AK217" s="11">
+      <c t="s" r="AL217" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AL217" s="11">
+      <c t="s" r="AM217" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AM217" s="11">
+      <c t="s" r="AN217" s="11">
         <v>336</v>
       </c>
-      <c t="s" r="AN217" s="11">
+      <c t="s" r="AO217" s="11">
         <v>337</v>
-      </c>
-      <c t="s" r="AO217" s="11">
-        <v>338</v>
       </c>
       <c r="AP217" s="12"/>
       <c t="s" r="AQ217" s="12">
@@ -31579,10 +33548,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX217" s="11">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c t="s" r="AY217" s="11">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AZ217" s="12"/>
       <c r="BA217" s="12"/>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-15).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-15).xlsx
@@ -938,34 +938,34 @@
     <t>215</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 4.932,90</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 4.936,16</t>
   </si>
   <si>
     <t>55.0</t>
   </si>
   <si>
-    <t>35.7</t>
-  </si>
-  <si>
-    <t>5.32</t>
-  </si>
-  <si>
-    <t>19.6</t>
-  </si>
-  <si>
-    <t>7.9</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>40.2%</t>
-  </si>
-  <si>
-    <t>18.9%</t>
+    <t>35.4</t>
+  </si>
+  <si>
+    <t>5.34</t>
+  </si>
+  <si>
+    <t>19.5</t>
+  </si>
+  <si>
+    <t>7.8</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>39.9%</t>
+  </si>
+  <si>
+    <t>18.8%</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -983,40 +983,40 @@
     <t>7.3%</t>
   </si>
   <si>
-    <t>3.3%</t>
+    <t>3.2%</t>
   </si>
   <si>
     <t>5.4%</t>
   </si>
   <si>
-    <t>1536.0</t>
-  </si>
-  <si>
-    <t>1235.0</t>
-  </si>
-  <si>
-    <t>86.0</t>
+    <t>1550.0</t>
+  </si>
+  <si>
+    <t>1246.0</t>
+  </si>
+  <si>
+    <t>88.0</t>
   </si>
   <si>
     <t>16.0</t>
   </si>
   <si>
-    <t>257.0</t>
-  </si>
-  <si>
-    <t>100.0</t>
+    <t>261.0</t>
+  </si>
+  <si>
+    <t>101.0</t>
   </si>
   <si>
     <t>11.0</t>
   </si>
   <si>
-    <t>479.0</t>
+    <t>484.0</t>
   </si>
   <si>
     <t>213.0</t>
   </si>
   <si>
-    <t>353.0</t>
+    <t>355.0</t>
   </si>
   <si>
     <t>0.6%</t>
@@ -7725,7 +7725,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7755,35 +7755,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>5840.1599999999999</v>
+      </c>
+      <c r="N42" s="6">
+        <v>46</v>
+      </c>
+      <c r="O42" s="6">
+        <v>24</v>
+      </c>
+      <c r="P42" s="7">
+        <v>6.0287500000000005</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>18.256249999999998</v>
+      </c>
+      <c r="R42" s="8">
+        <v>4.1937500000000005</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -9364,7 +9422,9 @@
       <c r="N53" s="6">
         <v>53</v>
       </c>
-      <c r="O53" s="6"/>
+      <c r="O53" s="6">
+        <v>25</v>
+      </c>
       <c r="P53" s="7">
         <v>4.3872549019607847</v>
       </c>
@@ -9374,31 +9434,75 @@
       <c r="R53" s="8">
         <v>2.901332</v>
       </c>
-      <c r="S53" s="8"/>
+      <c r="S53" s="8">
+        <v>7</v>
+      </c>
       <c r="T53" s="9">
         <v>0.80000000000000004</v>
       </c>
-      <c r="U53" s="9"/>
-      <c r="V53" s="9"/>
-      <c r="W53" s="9"/>
-      <c r="X53" s="9"/>
-      <c r="Y53" s="9"/>
-      <c r="Z53" s="9"/>
-      <c r="AA53" s="9"/>
-      <c r="AB53" s="9"/>
-      <c r="AC53" s="9"/>
-      <c r="AD53" s="6"/>
-      <c r="AE53" s="6"/>
-      <c r="AF53" s="6"/>
-      <c r="AG53" s="6"/>
-      <c r="AH53" s="6"/>
-      <c r="AI53" s="6"/>
-      <c r="AJ53" s="6"/>
-      <c r="AK53" s="6"/>
-      <c r="AL53" s="6"/>
-      <c r="AM53" s="6"/>
-      <c r="AN53" s="9"/>
-      <c r="AO53" s="6"/>
+      <c r="U53" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="V53" s="9">
+        <v>0</v>
+      </c>
+      <c r="W53" s="9">
+        <v>0</v>
+      </c>
+      <c r="X53" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Y53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE53" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP53" s="4">
         <v>58</v>
       </c>
@@ -14046,7 +14150,7 @@
         <v>19687</v>
       </c>
       <c r="B85" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C85" s="4">
         <v>51</v>
@@ -14076,35 +14180,93 @@
         <v>58</v>
       </c>
       <c r="L85" s="4"/>
-      <c r="M85" s="5"/>
-      <c r="N85" s="6"/>
-      <c r="O85" s="6"/>
-      <c r="P85" s="7"/>
-      <c r="Q85" s="8"/>
-      <c r="R85" s="8"/>
-      <c r="S85" s="8"/>
-      <c r="T85" s="9"/>
-      <c r="U85" s="9"/>
-      <c r="V85" s="9"/>
-      <c r="W85" s="9"/>
-      <c r="X85" s="9"/>
-      <c r="Y85" s="9"/>
-      <c r="Z85" s="9"/>
-      <c r="AA85" s="9"/>
-      <c r="AB85" s="9"/>
-      <c r="AC85" s="9"/>
-      <c r="AD85" s="6"/>
-      <c r="AE85" s="6"/>
-      <c r="AF85" s="6"/>
-      <c r="AG85" s="6"/>
-      <c r="AH85" s="6"/>
-      <c r="AI85" s="6"/>
-      <c r="AJ85" s="6"/>
-      <c r="AK85" s="6"/>
-      <c r="AL85" s="6"/>
-      <c r="AM85" s="6"/>
-      <c r="AN85" s="9"/>
-      <c r="AO85" s="6"/>
+      <c r="M85" s="5">
+        <v>4630.8000000000002</v>
+      </c>
+      <c r="N85" s="6">
+        <v>57</v>
+      </c>
+      <c r="O85" s="6">
+        <v>8</v>
+      </c>
+      <c r="P85" s="7">
+        <v>8.0905235294117634</v>
+      </c>
+      <c r="Q85" s="8">
+        <v>17.4020875</v>
+      </c>
+      <c r="R85" s="8">
+        <v>8.7861166666666666</v>
+      </c>
+      <c r="S85" s="8">
+        <v>7</v>
+      </c>
+      <c r="T85" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="U85" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="V85" s="9">
+        <v>0</v>
+      </c>
+      <c r="W85" s="9">
+        <v>0</v>
+      </c>
+      <c r="X85" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="Y85" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="Z85" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="AB85" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE85" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF85" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI85" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ85" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL85" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP85" s="4">
         <v>58</v>
       </c>
@@ -18573,33 +18735,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>24</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -28936,7 +29144,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>51</v>
@@ -31644,7 +31852,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>51</v>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-15).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-15).xlsx
@@ -938,19 +938,19 @@
     <t>215</t>
   </si>
   <si>
-    <t>29</t>
+    <t>23</t>
   </si>
   <si>
-    <t>R$ 4.936,16</t>
+    <t>R$ 4.921,24</t>
   </si>
   <si>
-    <t>55.0</t>
+    <t>54.5</t>
   </si>
   <si>
-    <t>35.4</t>
+    <t>35.7</t>
   </si>
   <si>
-    <t>5.34</t>
+    <t>5.32</t>
   </si>
   <si>
     <t>19.5</t>
@@ -959,13 +959,13 @@
     <t>7.8</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>39.9%</t>
+    <t>40.1%</t>
   </si>
   <si>
-    <t>18.8%</t>
+    <t>18.4%</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -974,25 +974,25 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>3.9%</t>
+    <t>3.8%</t>
   </si>
   <si>
     <t>1.5%</t>
   </si>
   <si>
-    <t>7.3%</t>
+    <t>7.2%</t>
   </si>
   <si>
     <t>3.2%</t>
   </si>
   <si>
-    <t>5.4%</t>
+    <t>5.2%</t>
   </si>
   <si>
-    <t>1550.0</t>
+    <t>1565.0</t>
   </si>
   <si>
-    <t>1246.0</t>
+    <t>1261.0</t>
   </si>
   <si>
     <t>88.0</t>
@@ -1001,19 +1001,19 @@
     <t>16.0</t>
   </si>
   <si>
-    <t>261.0</t>
+    <t>263.0</t>
   </si>
   <si>
     <t>101.0</t>
   </si>
   <si>
-    <t>11.0</t>
+    <t>13.0</t>
   </si>
   <si>
-    <t>484.0</t>
+    <t>490.0</t>
   </si>
   <si>
-    <t>213.0</t>
+    <t>217.0</t>
   </si>
   <si>
     <t>355.0</t>
@@ -1022,7 +1022,7 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>37.0</t>
+    <t>38.0</t>
   </si>
   <si>
     <t>1</t>
@@ -2209,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,35 +2239,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>12108.67</v>
+      </c>
+      <c r="N6" s="6">
+        <v>126</v>
+      </c>
+      <c r="O6" s="6">
+        <v>97</v>
+      </c>
+      <c r="P6" s="7">
+        <v>5.7252100840336126</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>16.129553608247424</v>
+      </c>
+      <c r="R6" s="8">
+        <v>3.25</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.45360824742268041</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.061855670103092786</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0.010309278350515464</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.010309278350515464</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.041237113402061855</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -9132,7 +9190,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9162,14 +9220,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>687.13</v>
+      </c>
+      <c r="N51" s="6">
+        <v>7</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>3.2166714285714284</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>26.62223333333333</v>
+      </c>
+      <c r="R51" s="8">
+        <v>16.877766666666666</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -10201,33 +10271,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>52</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -24112,7 +24228,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -24142,35 +24258,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>3158.3899999999999</v>
+      </c>
+      <c r="N151" s="6">
+        <v>34</v>
+      </c>
+      <c r="O151" s="6">
+        <v>29</v>
+      </c>
+      <c r="P151" s="7">
+        <v>3.9076199999999996</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>13.068965517241379</v>
+      </c>
+      <c r="R151" s="8">
+        <v>2.6691370370370371</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.82758620689655171</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.20689655172413793</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.13793103448275862</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -24994,7 +25168,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -25024,35 +25198,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>3552.0100000000002</v>
+      </c>
+      <c r="N157" s="6">
+        <v>41</v>
+      </c>
+      <c r="O157" s="6">
+        <v>32</v>
+      </c>
+      <c r="P157" s="7">
+        <v>5.5991461538461538</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>16.143228125</v>
+      </c>
+      <c r="R157" s="8">
+        <v>3.2890625</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.40625</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -25093,7 +25325,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25123,8 +25355,12 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
+      <c r="M158" s="5">
+        <v>0</v>
+      </c>
+      <c r="N158" s="6">
+        <v>0</v>
+      </c>
       <c r="O158" s="6"/>
       <c r="P158" s="7"/>
       <c r="Q158" s="8"/>
@@ -26128,7 +26364,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26158,35 +26394,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>2325.0999999999999</v>
+      </c>
+      <c r="N165" s="6">
+        <v>27</v>
+      </c>
+      <c r="O165" s="6">
+        <v>23</v>
+      </c>
+      <c r="P165" s="7">
+        <v>4.0524703703703704</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>12.122465217391305</v>
+      </c>
+      <c r="R165" s="8">
+        <v>1.008695652173913</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>1</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
